--- a/data/processed/times.xlsx
+++ b/data/processed/times.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,32 +429,17 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>nome_curto</t>
+          <t>sigla</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>sigla</t>
+          <t>fundacao</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>pais</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>ano_fundacao</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
           <t>estadio</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>escudo_url</t>
         </is>
       </c>
     </row>
@@ -469,30 +454,15 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fluminense</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
           <t>FLU</t>
         </is>
       </c>
+      <c r="D2" t="n">
+        <v>1902</v>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1902</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
           <t>Estadio Jornalista Mário Filho</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/1765.png</t>
         </is>
       </c>
     </row>
@@ -507,30 +477,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mineiro</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
           <t>CAM</t>
         </is>
       </c>
+      <c r="D3" t="n">
+        <v>1908</v>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>1908</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
           <t>Estádio Raimundo Sampaio</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/1766.png</t>
         </is>
       </c>
     </row>
@@ -545,30 +500,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Grêmio</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
           <t>FBP</t>
         </is>
       </c>
+      <c r="D4" t="n">
+        <v>1903</v>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1903</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
           <t>Arena do Grêmio</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/1767.png</t>
         </is>
       </c>
     </row>
@@ -583,30 +523,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Paranaense</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
           <t>CAP</t>
         </is>
       </c>
+      <c r="D5" t="n">
+        <v>1924</v>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1924</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
           <t>Estádio Joaquim Américo Guimarães</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/1768.png</t>
         </is>
       </c>
     </row>
@@ -621,30 +546,15 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
           <t>PAL</t>
         </is>
       </c>
+      <c r="D6" t="n">
+        <v>1914</v>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1914</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
           <t>Allianz Parque</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/1769.png</t>
         </is>
       </c>
     </row>
@@ -659,30 +569,15 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Botafogo</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
           <t>BOT</t>
         </is>
       </c>
+      <c r="D7" t="n">
+        <v>1904</v>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1904</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
           <t>Estádio Nilton Santos</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/1770.png</t>
         </is>
       </c>
     </row>
@@ -697,30 +592,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
           <t>CRU</t>
         </is>
       </c>
+      <c r="D8" t="n">
+        <v>1921</v>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>1921</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
           <t>Estádio Governador Magalhães Pinto</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/1771.png</t>
         </is>
       </c>
     </row>
@@ -735,30 +615,15 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
           <t>CHA</t>
         </is>
       </c>
+      <c r="D9" t="n">
+        <v>1973</v>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1973</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
           <t>Arena Condá</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/1772_large.png</t>
         </is>
       </c>
     </row>
@@ -773,30 +638,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
           <t>PAU</t>
         </is>
       </c>
+      <c r="D10" t="n">
+        <v>1930</v>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1930</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
           <t>Estádio do Morumbi</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/1776.png</t>
         </is>
       </c>
     </row>
@@ -811,30 +661,15 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bahia</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
           <t>BAH</t>
         </is>
       </c>
+      <c r="D11" t="n">
+        <v>1931</v>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1931</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
           <t>Estádio Governador Roberto Santos</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/1777.png</t>
         </is>
       </c>
     </row>
@@ -849,30 +684,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Corinthians</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
           <t>COR</t>
         </is>
       </c>
+      <c r="D12" t="n">
+        <v>1910</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1910</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
           <t>Neo Química Arena</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/1779.png</t>
         </is>
       </c>
     </row>
@@ -887,30 +707,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
           <t>VAS</t>
         </is>
       </c>
+      <c r="D13" t="n">
+        <v>1898</v>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>1898</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
           <t>Estádio Club de Regatas Vasco da Gama</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/1780.png</t>
         </is>
       </c>
     </row>
@@ -925,30 +730,15 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vitória</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
           <t>VIT</t>
         </is>
       </c>
+      <c r="D14" t="n">
+        <v>1899</v>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1899</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
           <t>Estádio Manoel Barradas</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/1782.png</t>
         </is>
       </c>
     </row>
@@ -963,30 +753,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
           <t>FLA</t>
         </is>
       </c>
+      <c r="D15" t="n">
+        <v>1919</v>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>1919</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
           <t>Estadio Jornalista Mário Filho</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/1783.png</t>
         </is>
       </c>
     </row>
@@ -1001,30 +776,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Coritiba</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
           <t>COR</t>
         </is>
       </c>
+      <c r="D16" t="n">
+        <v>1909</v>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>1909</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
           <t>Estádio Major Antônio Couto Pereira</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/4241.png</t>
         </is>
       </c>
     </row>
@@ -1039,30 +799,15 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bragantino</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
           <t>RBB</t>
         </is>
       </c>
+      <c r="D17" t="n">
+        <v>1928</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>1928</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
           <t>Estádio Nabi Abi Chedid</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/4286.png</t>
         </is>
       </c>
     </row>
@@ -1077,30 +822,15 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Clube do Remo</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
           <t>CRE</t>
         </is>
       </c>
+      <c r="D18" t="n">
+        <v>1905</v>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>1905</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
           <t>Estádio Estadual Jornalista Edgar Augusto Proença</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/4287.png</t>
         </is>
       </c>
     </row>
@@ -1115,30 +845,15 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mirassol</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
           <t>MIR</t>
         </is>
       </c>
+      <c r="D19" t="n">
+        <v>1925</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>1925</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
           <t>Estádio José Maria de Campos Maia</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/4364.png</t>
         </is>
       </c>
     </row>
@@ -1153,30 +868,15 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
           <t>SCI</t>
         </is>
       </c>
+      <c r="D20" t="n">
+        <v>1909</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>1909</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
           <t>Estádio José Pinheiro Borba</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/6684.png</t>
         </is>
       </c>
     </row>
@@ -1191,30 +891,15 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Santos</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
           <t>SAN</t>
         </is>
       </c>
+      <c r="D21" t="n">
+        <v>1912</v>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1912</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
           <t>Estádio Urbano Caldeira</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/6685.png</t>
         </is>
       </c>
     </row>
